--- a/mlef_pipeline/results/OS_24/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,58 +552,58 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6412066752246469</v>
+        <v>0.6428112965340179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08797563241186179</v>
+        <v>0.0814084757641762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4296147404197339</v>
+        <v>0.4403446864431684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1110150470245704</v>
+        <v>0.07293005823848635</v>
       </c>
       <c r="F2" t="n">
-        <v>0.624134721164424</v>
+        <v>0.5055301684014556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2411440597694226</v>
+        <v>0.202251438781948</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4774718648335422</v>
+        <v>0.5539785351084129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1710573611352817</v>
+        <v>0.1629022823170606</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6729651162790697</v>
+        <v>0.75</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1652912574802605</v>
+        <v>0.1579602856580887</v>
       </c>
       <c r="L2" t="n">
-        <v>0.533801580333626</v>
+        <v>0.4400345125107852</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4651162790697674</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8125</v>
+        <v>0.61875</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1858847002532018</v>
+        <v>0.3260297017211609</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.4272727272727272</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6875</v>
+        <v>0.3125</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
@@ -809,9 +809,7 @@
       <c r="N5" t="n">
         <v>0.84</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0.5636363636363637</v>
@@ -842,56 +840,54 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.56921768707483</v>
+        <v>0.6654761904761906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1258474805819027</v>
+        <v>0.1355465001659674</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4316511608482946</v>
+        <v>0.5069482366708753</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09061686509608968</v>
+        <v>0.2156415392268149</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3312629399585921</v>
+        <v>0.6467505241090147</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3841168415701531</v>
+        <v>0.296358507109082</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7377752682100508</v>
+        <v>0.6282011895923471</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3142838740358642</v>
+        <v>0.340770826820937</v>
       </c>
       <c r="J6" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2350181838751005</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6674132138857782</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.625</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.216911131941058</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.2792022792022792</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.8571428571428572</v>
-      </c>
+        <v>0.76</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2857142857142857</v>
       </c>
       <c r="T6" t="n">
         <v>11</v>
@@ -951,9 +947,7 @@
       <c r="N7" t="n">
         <v>0.92</v>
       </c>
-      <c r="O7" t="n">
-        <v>0.8571428571428572</v>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0.4666666666666667</v>
@@ -1022,9 +1016,7 @@
       <c r="N8" t="n">
         <v>0.6</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.5714285714285714</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0.3333333333333333</v>
@@ -1046,6 +1038,268 @@
       </c>
       <c r="W8" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.5545070588930239</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1482590771958059</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4027511698320657</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6447933440687064</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1020655571893118</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2690438133815619</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>54</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.407986111111111</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.322928178314778</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3328936999709676</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1940480982966918</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3552467795046459</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4775480354899121</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>54</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9652173913043479</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04187592654565658</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4526323349852762</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2312863379479618</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4112975875177065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5234441602728047</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3259514360659927</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.366681280452084</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5112781954887218</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>51</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2978260869565217</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2766570266009259</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.192427473913542</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2460570576500215</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4897959183673469</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.499895865874118</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3265306122448979</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4689438895133085</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>51</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/mlef_pipeline/results/OS_24/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_24/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,130 +548,757 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>0.6428112965340179</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0814084757641762</v>
+      </c>
       <c r="D2" t="n">
-        <v>0.5545070588930239</v>
+        <v>0.4403446864431684</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1482590771958059</v>
+        <v>0.07293005823848635</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.5055301684014556</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4027511698320657</v>
+        <v>0.202251438781948</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6447933440687064</v>
+        <v>0.5539785351084129</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1020655571893118</v>
+        <v>0.1629022823170606</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7499999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2690438133815619</v>
+        <v>0.1579602856580887</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7636363636363637</v>
+        <v>0.4400345125107852</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>0.2790697674418605</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.61875</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3260297017211609</v>
+      </c>
       <c r="Q2" t="n">
-        <v>0.4</v>
+        <v>0.4272727272727272</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3125</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>54</v>
+        <v>303</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>RWD_DP</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7861142217245241</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.09814408900045168</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5519882177544031</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1324040874547249</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5163716814159293</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3091125233930385</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6872875403848855</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1154283915119827</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6333333333333334</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4058579773750778</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6833333333333333</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3233775590149248</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>113</v>
+      </c>
+      <c r="V3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RWD_DP/rwd-only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6131019036954087</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1375953476488664</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2451023888505658</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1601817605162999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3451327433628318</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4754115404801166</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4695322376738305</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4595523747469447</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8666666666666668</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1602894919831171</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5790917220437068</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>113</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8816326530612244</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07753467963323102</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6930289999546734</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.110238468274598</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8339544513457556</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2064679485981686</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7984889218503755</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1273161870415554</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5549999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2875601345621261</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0.5636363636363637</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>161</v>
+      </c>
+      <c r="V5" t="n">
+        <v>33</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6654761904761906</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1355465001659674</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5069482366708753</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2156415392268149</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6467505241090147</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.296358507109082</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6282011895923471</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.340770826820937</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2350181838751005</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6674132138857782</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>161</v>
+      </c>
+      <c r="V6" t="n">
+        <v>33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7894927536231884</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0887373949157173</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.594382854275833</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1240794698154495</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5556962025316455</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2724696408326121</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.787560089846128</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1350702052302841</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2109022253003471</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.509090909090909</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>158</v>
+      </c>
+      <c r="V7" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5942028985507246</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.142090275913568</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3862724374532429</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1254387315928437</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.416025641025641</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2998924582613324</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5294712335757111</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2434591527597844</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2037303313808414</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4260869565217391</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>158</v>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0.5545070588930239</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1482590771958059</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4027511698320657</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6447933440687064</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1020655571893118</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7499999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2690438133815619</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7636363636363637</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>54</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B10" t="n">
         <v>0.546875</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C10" t="n">
         <v>0.2731941098474786</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D10" t="n">
         <v>0.2040768588137009</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E10" t="n">
         <v>0.2437731408533252</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F10" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G10" t="n">
         <v>0.4985185152621431</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H10" t="n">
         <v>0.3653846153846154</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I10" t="n">
         <v>0.4815378471364967</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J10" t="n">
         <v>0.5</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
         <v>0.4090909090909091</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="n">
         <v>11</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U10" t="n">
         <v>54</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V10" t="n">
         <v>13</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.9652173913043479</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04187592654565658</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4526323349852762</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2312863379479618</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7843137254901961</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4112975875177065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5234441602728047</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3259514360659927</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.366681280452084</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5112781954887218</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>51</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2978260869565217</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2766570266009259</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.192427473913542</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2460570576500215</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4897959183673469</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.499895865874118</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3265306122448979</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4689438895133085</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>51</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
         <v>6</v>
       </c>
     </row>
